--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>93.23999999999999</v>
+        <v>89.67</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>43.05</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.166</v>
+        <v>1.038</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04998000144958496</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093224.994192799</v>
+        <v>3093225.090909091</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>43.05</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>133163336</v>
+        <v>136101904</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.33</v>
+        <v>11.58</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>142706592</v>
+        <v>143791056</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.707649999999999</v>
+        <v>9.781421</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>4.28</v>
+        <v>4.288</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>103898800</v>
+        <v>105009472</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>8.298387999999999</v>
+        <v>8.387097000000001</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>3.943</v>
+        <v>3.963</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>100533632</v>
+        <v>100015672</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>8.853007</v>
+        <v>8.880846999999999</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>4.56</v>
+        <v>4.578</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>142572640</v>
+        <v>144545344</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>9.9375</v>
+        <v>9.975247</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.758</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="10">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>115178536</v>
+        <v>116618272</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>8.745981</v>
+        <v>8.883870999999999</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>125784000</v>
+        <v>118796000</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>10.6508875</v>
+        <v>10.059172</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.573</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="13">
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>111304208</v>
+        <v>112673720</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>11.580312</v>
+        <v>11.692507</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>2.186</v>
+        <v>2.213</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>89.67</v>
+        <v>86.56</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>44</v>
+        <v>45.99</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.038</v>
+        <v>0.882</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.25</v>
+        <v>0.417</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.05245999813079834</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093225.090909091</v>
+        <v>3093225.135899108</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>44</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="38">
@@ -1520,190 +1520,186 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>136101904</v>
+        <v>142257424</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.58</v>
+        <v>12.2</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHBH</t>
+          <t>ASRV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Croghan Bancshares, Inc.</t>
+          <t>AmeriServ Financial Inc.</t>
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>143791056</v>
+        <v>75557736</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.781421</v>
+        <v>8.725490000000001</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>4.288</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CNBB</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CNB Community Bancorp Inc.</t>
+          <t>Franklin Financial Services Cor</t>
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>105009472</v>
+        <v>282798720</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>8.387097000000001</v>
+        <v>11.468978</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>3.963</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CYVF</t>
+          <t>FXNC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crystal Valley Financial Corp.</t>
+          <t>First National Corporation</t>
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>100015672</v>
+        <v>267390544</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>8.880846999999999</v>
+        <v>12.320832</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>4.578</v>
+        <v>1.597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FMBM</t>
+          <t>HFBL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F &amp; M Bank Corp.</t>
+          <t>Home Federal Bancorp, Inc. of L</t>
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>144545344</v>
+        <v>73219152</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>9.975247</v>
+        <v>11.960396</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.68</v>
+        <v>1.762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JDVB</t>
+          <t>PFIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JD Bancshares, Inc.</t>
+          <t>Peoples Financial Services Corp</t>
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>126833112</v>
+        <v>680855104</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.462915000000001</v>
+        <v>12.038053</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>1.484</v>
+        <v>4.018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JFBC</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeffersonville Bancorp</t>
+          <t>Provident Financial Holdings, I</t>
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>116618272</v>
+        <v>114206112</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>8.883870999999999</v>
+        <v>17.786407</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>0.917</v>
+        <v>5.544</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MPCB</t>
+          <t>PSBQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mountain Pacific Bancorp Inc.</t>
+          <t>PSB Holdings Inc.</t>
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>118796000</v>
+        <v>201278976</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>10.059172</v>
+        <v>14.465318</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.398</v>
+        <v>6.138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OXBC</t>
+          <t>SBMW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oxford Bank Corporation</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="n">
-        <v>112673720</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <v>11.692507</v>
-      </c>
+          <t>Security Midwest Bancorp, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>2.213</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="15">
@@ -1751,7 +1747,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>86.56</v>
+        <v>86.58</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>45.99</v>
+        <v>44.5</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.882</v>
+        <v>0.946</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.417</v>
+        <v>0.583</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05245999813079834</v>
+        <v>0.0524399995803833</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093225.135899108</v>
+        <v>3093224.988764045</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>45.99</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>142257424</v>
+        <v>137648512</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>75557736</v>
+        <v>74538984</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>8.725490000000001</v>
+        <v>8.607843000000001</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>1.75</v>
+        <v>1.733</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>282798720</v>
+        <v>281673824</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.468978</v>
+        <v>11.423357</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>5.18</v>
+        <v>5.144</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>267390544</v>
+        <v>266395840</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12.320832</v>
+        <v>12.274999</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.597</v>
+        <v>1.547</v>
       </c>
     </row>
     <row r="9">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>680855104</v>
+        <v>673197184</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.038053</v>
+        <v>12.227273</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>4.018</v>
+        <v>3.922</v>
       </c>
     </row>
     <row r="11">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>114206112</v>
+        <v>113170496</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.786407</v>
+        <v>17.728155</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>5.544</v>
+        <v>5.511</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>201278976</v>
+        <v>201077904</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>14.465318</v>
+        <v>14.450867</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>6.138</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="13">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>86.58</v>
+        <v>86.63</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>44.5</v>
+        <v>45.99</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.946</v>
+        <v>0.884</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.583</v>
+        <v>0.417</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0524399995803833</v>
+        <v>0.05240000247955322</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093224.988764045</v>
+        <v>3093225.135899108</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>44.5</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>137648512</v>
+        <v>142257424</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>281673824</v>
+        <v>287073344</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.423357</v>
+        <v>11.642336</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>266395840</v>
+        <v>269832064</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12.274999</v>
+        <v>12.433332</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>673197184</v>
+        <v>687512000</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.227273</v>
+        <v>12.155752</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>113170496</v>
+        <v>112674680</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.728155</v>
+        <v>17.650486</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.767</v>
+        <v>0.833</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>86.63</v>
+        <v>88.28</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>45.99</v>
+        <v>44.755</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.884</v>
+        <v>0.973</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.417</v>
+        <v>0.583</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05105999946594238</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093225.135899108</v>
+        <v>3093225.248575578</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>45.99</v>
+        <v>44.755</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>142257424</v>
+        <v>138437296</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.2</v>
+        <v>11.87</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>74538984</v>
+        <v>78670040</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>8.607843000000001</v>
+        <v>9.084902</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>1.733</v>
+        <v>1.752</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>287073344</v>
+        <v>281943808</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.642336</v>
+        <v>11.434306</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>5.144</v>
+        <v>5.155</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>269832064</v>
+        <v>266667120</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12.433332</v>
+        <v>12.287499</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.547</v>
+        <v>1.543</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>73219152</v>
+        <v>73097928</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>11.960396</v>
+        <v>11.940595</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.762</v>
+        <v>1.757</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>687512000</v>
+        <v>686811264</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.155752</v>
+        <v>12.143363</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>3.922</v>
+        <v>3.964</v>
       </c>
     </row>
     <row r="11">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>112674680</v>
+        <v>112488744</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.650486</v>
+        <v>17.621359</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>5.511</v>
+        <v>5.488</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>201077904</v>
+        <v>207110240</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>14.450867</v>
+        <v>14.884393</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>5.99</v>
+        <v>5.997</v>
       </c>
     </row>
     <row r="13">
@@ -1699,7 +1699,7 @@
       <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>3.14</v>
+        <v>3.122</v>
       </c>
     </row>
     <row r="15">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.833</v>
+        <v>0.733</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>88.28</v>
+        <v>88.38</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>44.755</v>
+        <v>46.85</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.973</v>
+        <v>0.886</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.583</v>
+        <v>0.333</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05105999946594238</v>
+        <v>0.05098000049591064</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093225.248575578</v>
+        <v>3093224.8452508</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>44.755</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>138437296</v>
+        <v>144917584</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.87</v>
+        <v>12.43</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>78670040</v>
+        <v>77085880</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.084902</v>
+        <v>8.901961</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>1.752</v>
+        <v>1.775</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>281943808</v>
+        <v>282348768</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.434306</v>
+        <v>11.45073</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>5.155</v>
+        <v>5.152</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>266667120</v>
+        <v>267300112</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12.287499</v>
+        <v>12.316666</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.543</v>
+        <v>1.557</v>
       </c>
     </row>
     <row r="9">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>686811264</v>
+        <v>683708096</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.143363</v>
+        <v>12.088496</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>3.964</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="11">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>5.488</v>
+        <v>5.494</v>
       </c>
     </row>
     <row r="12">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>5.997</v>
+        <v>6.102</v>
       </c>
     </row>
     <row r="13">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.333</v>
+        <v>0.833</v>
       </c>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>88.38</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.886</v>
+        <v>0.873</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0514799976348877</v>
       </c>
     </row>
     <row r="6">
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>77085880</v>
+        <v>75730928</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>8.901961</v>
+        <v>8.74549</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>282348768</v>
+        <v>280998912</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.45073</v>
+        <v>11.395986</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>73097928</v>
+        <v>73037320</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>11.940595</v>
+        <v>11.930694</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>683708096</v>
+        <v>677201344</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.088496</v>
+        <v>11.973452</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>112488744</v>
+        <v>112426760</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.621359</v>
+        <v>17.61165</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>87.76000000000001</v>
+        <v>88.02</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.873</v>
+        <v>0.879</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0514799976348877</v>
+        <v>0.05126999855041504</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>75730928</v>
+        <v>78953600</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>8.74549</v>
+        <v>9.117647</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>1.775</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>280998912</v>
+        <v>284666048</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.395986</v>
+        <v>11.544708</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>5.152</v>
+        <v>5.131</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>267300112</v>
+        <v>269018208</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12.316666</v>
+        <v>12.395833</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.557</v>
+        <v>1.542</v>
       </c>
     </row>
     <row r="9">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.757</v>
+        <v>1.754</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>677201344</v>
+        <v>685459840</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>11.973452</v>
+        <v>12.119469</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>3.978</v>
+        <v>3.944</v>
       </c>
     </row>
     <row r="11">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>112426760</v>
+        <v>112798640</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.61165</v>
+        <v>17.669905</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>5.494</v>
+        <v>5.488</v>
       </c>
     </row>
     <row r="12">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>6.102</v>
+        <v>5.954</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>88.02</v>
+        <v>88.28</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.879</v>
+        <v>0.884</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05126999855041504</v>
+        <v>0.05105999946594238</v>
       </c>
     </row>
     <row r="6">
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>78953600</v>
+        <v>80991112</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.117647</v>
+        <v>8.833333</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>284666048</v>
+        <v>282753728</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>11.544708</v>
+        <v>11.467154</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>5.131</v>
+        <v>5.154</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>269018208</v>
+        <v>264949024</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12.395833</v>
+        <v>12.208332</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>1.542</v>
+        <v>1.569</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>73037320</v>
+        <v>72734256</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>11.930694</v>
+        <v>11.881188</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.754</v>
+        <v>1.742</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>685459840</v>
+        <v>687512000</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.119469</v>
+        <v>12.155752</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>3.944</v>
+        <v>4.023</v>
       </c>
     </row>
     <row r="11">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>112798640</v>
+        <v>112519736</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.669905</v>
+        <v>17.626215</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>5.488</v>
+        <v>5.492</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>207110240</v>
+        <v>190018608</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>14.884393</v>
+        <v>13.656069</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>5.954</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="13">
